--- a/backend/assets/report-templates/employee-leave-report-with-return-taiwan.xlsx
+++ b/backend/assets/report-templates/employee-leave-report-with-return-taiwan.xlsx
@@ -23,12 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t xml:space="preserve">卡號：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A542</t>
   </si>
   <si>
     <t xml:space="preserve">單位：</t>
@@ -37,13 +34,7 @@
     <t xml:space="preserve">補休：</t>
   </si>
   <si>
-    <t xml:space="preserve"> 2025/07/24 ~ 2026/07/23</t>
-  </si>
-  <si>
     <t xml:space="preserve">姓名：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">林協志</t>
   </si>
   <si>
     <t xml:space="preserve">返台假時數：</t>
@@ -126,20 +117,18 @@
   <si>
     <t xml:space="preserve">總計</t>
   </si>
-  <si>
-    <t xml:space="preserve"> 2026/07/24 ~ 2027/07/23</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="0;\-0;;@"/>
-    <numFmt numFmtId="168" formatCode="mm\月dd\日;@"/>
+    <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="mm\月dd\日;@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -415,7 +404,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,11 +412,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -443,7 +432,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -752,28 +741,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
-        <v>1</v>
-      </c>
+      <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="9" t="n">
-        <v>5006</v>
-      </c>
+      <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
-      <c r="O2" s="9" t="s">
-        <v>4</v>
-      </c>
+      <c r="O2" s="9"/>
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
@@ -784,30 +767,28 @@
     <row r="3" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" s="12"/>
-      <c r="D3" s="8" t="s">
-        <v>6</v>
-      </c>
+      <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
       <c r="O3" s="9" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
@@ -841,123 +822,105 @@
     </row>
     <row r="5" customFormat="false" ht="28.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="I5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="J5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="K5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="L5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="M5" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="N5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="O5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="P5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="Q5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="R5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="S5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="T5" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="17" t="s">
+      <c r="U5" s="20" t="s">
         <v>26</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="T5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="U5" s="20" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
       <c r="O6" s="23"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
+      <c r="P6" s="24" t="n">
+        <f aca="false">O6</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="24" t="n">
+        <f aca="false">I3-P6</f>
+        <v>0</v>
+      </c>
       <c r="R6" s="23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="S6" s="24" t="n">
-        <f aca="false">O6</f>
-        <v>36</v>
+        <f aca="false">R6</f>
+        <v>0</v>
       </c>
       <c r="T6" s="24" t="n">
-        <f aca="false">O3-P6</f>
-        <v>56</v>
+        <f aca="false">O3-S6</f>
+        <v>0</v>
       </c>
       <c r="U6" s="25"/>
     </row>
@@ -1005,18 +968,24 @@
         <v>0</v>
       </c>
       <c r="O7" s="23"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
+      <c r="P7" s="24" t="n">
+        <f aca="false">P6+O7</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="24" t="n">
+        <f aca="false">I3-P7</f>
+        <v>0</v>
+      </c>
       <c r="R7" s="23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S7" s="24" t="n">
-        <f aca="false">P6+O7</f>
-        <v>44</v>
+        <f aca="false">S6+R7</f>
+        <v>0</v>
       </c>
       <c r="T7" s="24" t="n">
-        <f aca="false">O3-P7</f>
-        <v>56</v>
+        <f aca="false">O3-S7</f>
+        <v>0</v>
       </c>
       <c r="U7" s="25"/>
     </row>
@@ -1064,18 +1033,24 @@
         <v>0</v>
       </c>
       <c r="O8" s="23"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
+      <c r="P8" s="24" t="n">
+        <f aca="false">P7+O8</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="24" t="n">
+        <f aca="false">I3-P8</f>
+        <v>0</v>
+      </c>
       <c r="R8" s="23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S8" s="24" t="n">
-        <f aca="false">P7+O8</f>
-        <v>52</v>
+        <f aca="false">O3-R8</f>
+        <v>0</v>
       </c>
       <c r="T8" s="24" t="n">
-        <f aca="false">O3-P8</f>
-        <v>56</v>
+        <f aca="false">O3-S8</f>
+        <v>0</v>
       </c>
       <c r="U8" s="25"/>
     </row>
@@ -1123,18 +1098,24 @@
         <v>0</v>
       </c>
       <c r="O9" s="23"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
+      <c r="P9" s="24" t="n">
+        <f aca="false">P8+O9</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="24" t="n">
+        <f aca="false">I3-P9</f>
+        <v>0</v>
+      </c>
       <c r="R9" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S9" s="24" t="n">
-        <f aca="false">P8+O9</f>
-        <v>56</v>
+        <f aca="false">O3-R9</f>
+        <v>0</v>
       </c>
       <c r="T9" s="24" t="n">
-        <f aca="false">O3-P9</f>
-        <v>56</v>
+        <f aca="false">O3-S9</f>
+        <v>0</v>
       </c>
       <c r="U9" s="25"/>
     </row>
@@ -1149,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E10" s="22" t="n">
         <v>0</v>
@@ -1182,18 +1163,24 @@
         <v>0</v>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
+      <c r="P10" s="24" t="n">
+        <f aca="false">P9+O10</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="24" t="n">
+        <f aca="false">I3-P10</f>
+        <v>0</v>
+      </c>
       <c r="R10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="24" t="n">
-        <f aca="false">P9+O10</f>
-        <v>56</v>
+        <f aca="false">O3-R10</f>
+        <v>0</v>
       </c>
       <c r="T10" s="24" t="n">
-        <f aca="false">O3-P10</f>
-        <v>56</v>
+        <f aca="false">O3-S10</f>
+        <v>0</v>
       </c>
       <c r="U10" s="25"/>
     </row>
@@ -1208,7 +1195,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="22" t="n">
         <v>0</v>
@@ -1241,18 +1228,24 @@
         <v>0</v>
       </c>
       <c r="O11" s="23"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
+      <c r="P11" s="24" t="n">
+        <f aca="false">P10+O11</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="24" t="n">
+        <f aca="false">I3-P11</f>
+        <v>0</v>
+      </c>
       <c r="R11" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="24" t="n">
-        <f aca="false">P10+O11</f>
-        <v>56</v>
+        <f aca="false">O3-R11</f>
+        <v>0</v>
       </c>
       <c r="T11" s="24" t="n">
-        <f aca="false">O3-P11</f>
-        <v>56</v>
+        <f aca="false">O3-S11</f>
+        <v>0</v>
       </c>
       <c r="U11" s="25"/>
     </row>
@@ -1267,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" s="22" t="n">
         <v>0</v>
@@ -1300,18 +1293,24 @@
         <v>0</v>
       </c>
       <c r="O12" s="23"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
+      <c r="P12" s="24" t="n">
+        <f aca="false">P11+O12</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="24" t="n">
+        <f aca="false">I3-P12</f>
+        <v>0</v>
+      </c>
       <c r="R12" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S12" s="24" t="n">
-        <f aca="false">P11+O12</f>
-        <v>56</v>
+        <f aca="false">O3-R12</f>
+        <v>0</v>
       </c>
       <c r="T12" s="24" t="n">
-        <f aca="false">O3-P12</f>
-        <v>56</v>
+        <f aca="false">O3-S12</f>
+        <v>0</v>
       </c>
       <c r="U12" s="25"/>
     </row>
@@ -1355,18 +1354,24 @@
         <v>0</v>
       </c>
       <c r="O13" s="23"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
+      <c r="P13" s="24" t="n">
+        <f aca="false">P12+O13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="24" t="n">
+        <f aca="false">I3-P13</f>
+        <v>0</v>
+      </c>
       <c r="R13" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S13" s="24" t="n">
-        <f aca="false">P12+O13</f>
-        <v>56</v>
+        <f aca="false">O3-R13</f>
+        <v>0</v>
       </c>
       <c r="T13" s="24" t="n">
-        <f aca="false">O3-P13</f>
-        <v>56</v>
+        <f aca="false">O3-S13</f>
+        <v>0</v>
       </c>
       <c r="U13" s="25"/>
     </row>
@@ -1410,18 +1415,24 @@
         <v>0</v>
       </c>
       <c r="O14" s="23"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
+      <c r="P14" s="24" t="n">
+        <f aca="false">P13+O14</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="24" t="n">
+        <f aca="false">I3-P14</f>
+        <v>0</v>
+      </c>
       <c r="R14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S14" s="24" t="n">
-        <f aca="false">P13+O14</f>
-        <v>56</v>
+        <f aca="false">O3-R14</f>
+        <v>0</v>
       </c>
       <c r="T14" s="24" t="n">
-        <f aca="false">O3-P14</f>
-        <v>56</v>
+        <f aca="false">O3-S14</f>
+        <v>0</v>
       </c>
       <c r="U14" s="25"/>
     </row>
@@ -1465,18 +1476,24 @@
         <v>0</v>
       </c>
       <c r="O15" s="23"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
+      <c r="P15" s="24" t="n">
+        <f aca="false">P14+O15</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="24" t="n">
+        <f aca="false">I3-P15</f>
+        <v>0</v>
+      </c>
       <c r="R15" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="24" t="n">
-        <f aca="false">P14+O15</f>
-        <v>56</v>
+        <f aca="false">O3-R15</f>
+        <v>0</v>
       </c>
       <c r="T15" s="24" t="n">
-        <f aca="false">O3-P15</f>
-        <v>56</v>
+        <f aca="false">O3-S15</f>
+        <v>0</v>
       </c>
       <c r="U15" s="25"/>
     </row>
@@ -1520,18 +1537,24 @@
         <v>0</v>
       </c>
       <c r="O16" s="23"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
+      <c r="P16" s="24" t="n">
+        <f aca="false">P15+O16</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="24" t="n">
+        <f aca="false">I3-P16</f>
+        <v>0</v>
+      </c>
       <c r="R16" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="24" t="n">
-        <f aca="false">P15+O16</f>
-        <v>56</v>
+        <f aca="false">O3-R16</f>
+        <v>0</v>
       </c>
       <c r="T16" s="24" t="n">
-        <f aca="false">O3-P16</f>
-        <v>56</v>
+        <f aca="false">O3-S16</f>
+        <v>0</v>
       </c>
       <c r="U16" s="25"/>
     </row>
@@ -1575,18 +1598,24 @@
         <v>0</v>
       </c>
       <c r="O17" s="23"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
+      <c r="P17" s="24" t="n">
+        <f aca="false">P16+O17</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="24" t="n">
+        <f aca="false">I3-P17</f>
+        <v>0</v>
+      </c>
       <c r="R17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S17" s="24" t="n">
-        <f aca="false">P16+O17</f>
-        <v>56</v>
+        <f aca="false">O3-R17</f>
+        <v>0</v>
       </c>
       <c r="T17" s="24" t="n">
-        <f aca="false">O3-P17</f>
-        <v>56</v>
+        <f aca="false">O3-S17</f>
+        <v>0</v>
       </c>
       <c r="U17" s="25"/>
     </row>
@@ -1606,24 +1635,30 @@
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
       <c r="O18" s="23"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
+      <c r="P18" s="24" t="n">
+        <f aca="false">P17+O18</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="24" t="n">
+        <f aca="false">I3-P18</f>
+        <v>0</v>
+      </c>
       <c r="R18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S18" s="24" t="n">
-        <f aca="false">P17+O18</f>
-        <v>56</v>
+        <f aca="false">O15-R18</f>
+        <v>0</v>
       </c>
       <c r="T18" s="24" t="n">
-        <f aca="false">O3-P18</f>
-        <v>56</v>
+        <f aca="false">O3-S18</f>
+        <v>0</v>
       </c>
       <c r="U18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="28.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="29" t="n">
@@ -1632,7 +1667,7 @@
       </c>
       <c r="D19" s="29" t="n">
         <f aca="false">SUM(D6:D18)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E19" s="29" t="n">
         <f aca="false">SUM(E6:E18)</f>
@@ -1674,19 +1709,28 @@
         <f aca="false">SUM(N6:N18)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="30"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
+      <c r="O19" s="30" t="n">
+        <f aca="false">SUM(O6:O18)</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="31" t="n">
+        <f aca="false">P18</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="31" t="n">
+        <f aca="false">Q18</f>
+        <v>0</v>
+      </c>
       <c r="R19" s="30" t="n">
         <f aca="false">SUM(O6:O18)</f>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="S19" s="31" t="n">
-        <f aca="false">P18</f>
-        <v>56</v>
+        <f aca="false">S18</f>
+        <v>0</v>
       </c>
       <c r="T19" s="31" t="n">
-        <f aca="false">Q18</f>
+        <f aca="false">T18</f>
         <v>0</v>
       </c>
       <c r="U19" s="32"/>
@@ -1725,28 +1769,22 @@
         <v>0</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="8" t="s">
-        <v>1</v>
-      </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="9" t="n">
-        <v>5006</v>
-      </c>
+      <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
-      <c r="O22" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
@@ -1757,30 +1795,28 @@
     <row r="23" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C23" s="12"/>
-      <c r="D23" s="8" t="s">
-        <v>6</v>
-      </c>
+      <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="9" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
@@ -1814,67 +1850,67 @@
     </row>
     <row r="25" customFormat="false" ht="28.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="E25" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="F25" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="G25" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="H25" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="I25" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="J25" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="K25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="L25" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="M25" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="N25" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="17" t="s">
+      <c r="O25" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="17" t="s">
+      <c r="P25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N25" s="19" t="s">
+      <c r="Q25" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="O25" s="17" t="s">
+      <c r="R25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P25" s="18" t="s">
+      <c r="S25" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Q25" s="18" t="s">
+      <c r="T25" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="R25" s="17" t="s">
+      <c r="U25" s="20" t="s">
         <v>26</v>
-      </c>
-      <c r="S25" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="T25" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="U25" s="20" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="28.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1916,19 +1952,27 @@
       <c r="N26" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="24"/>
+      <c r="O26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="24" t="n">
+        <f aca="false">O26</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="24" t="n">
+        <f aca="false">I23-P26</f>
+        <v>0</v>
+      </c>
       <c r="R26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S26" s="24" t="n">
-        <f aca="false">O26</f>
+        <f aca="false">R26</f>
         <v>0</v>
       </c>
       <c r="T26" s="24" t="n">
-        <f aca="false">O23-P26</f>
-        <v>56</v>
+        <f aca="false">O23-S26</f>
+        <v>0</v>
       </c>
       <c r="U26" s="33"/>
     </row>
@@ -1971,19 +2015,27 @@
       <c r="N27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="23"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
+      <c r="O27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="24" t="n">
+        <f aca="false">P26+O27</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="24" t="n">
+        <f aca="false">I23-P27</f>
+        <v>0</v>
+      </c>
       <c r="R27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S27" s="24" t="n">
-        <f aca="false">P26+O27</f>
+        <f aca="false">S26+R27</f>
         <v>0</v>
       </c>
       <c r="T27" s="24" t="n">
-        <f aca="false">O23-P27</f>
-        <v>56</v>
+        <f aca="false">O23-S27</f>
+        <v>0</v>
       </c>
       <c r="U27" s="33"/>
     </row>
@@ -2026,19 +2078,27 @@
       <c r="N28" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="23"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
+      <c r="O28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="24" t="n">
+        <f aca="false">P27+O28</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="24" t="n">
+        <f aca="false">I23-P28</f>
+        <v>0</v>
+      </c>
       <c r="R28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S28" s="24" t="n">
-        <f aca="false">P27+O28</f>
+        <f aca="false">O23-R28</f>
         <v>0</v>
       </c>
       <c r="T28" s="24" t="n">
-        <f aca="false">O23-P28</f>
-        <v>56</v>
+        <f aca="false">O23-S28</f>
+        <v>0</v>
       </c>
       <c r="U28" s="33"/>
     </row>
@@ -2081,19 +2141,27 @@
       <c r="N29" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="23"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
+      <c r="O29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="24" t="n">
+        <f aca="false">P28+O29</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="24" t="n">
+        <f aca="false">I23-P29</f>
+        <v>0</v>
+      </c>
       <c r="R29" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="24" t="n">
-        <f aca="false">P28+O29</f>
+        <f aca="false">O23-R29</f>
         <v>0</v>
       </c>
       <c r="T29" s="24" t="n">
-        <f aca="false">O23-P29</f>
-        <v>56</v>
+        <f aca="false">O23-S29</f>
+        <v>0</v>
       </c>
       <c r="U29" s="33"/>
     </row>
@@ -2136,19 +2204,27 @@
       <c r="N30" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="23"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
+      <c r="O30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="24" t="n">
+        <f aca="false">P29+O30</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="24" t="n">
+        <f aca="false">I23-P30</f>
+        <v>0</v>
+      </c>
       <c r="R30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S30" s="24" t="n">
-        <f aca="false">P29+O30</f>
+        <f aca="false">O23-R30</f>
         <v>0</v>
       </c>
       <c r="T30" s="24" t="n">
-        <f aca="false">O23-P30</f>
-        <v>56</v>
+        <f aca="false">O23-S30</f>
+        <v>0</v>
       </c>
       <c r="U30" s="33"/>
     </row>
@@ -2191,19 +2267,27 @@
       <c r="N31" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="23"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
+      <c r="O31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="24" t="n">
+        <f aca="false">P30+O31</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24" t="n">
+        <f aca="false">I23-P31</f>
+        <v>0</v>
+      </c>
       <c r="R31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="24" t="n">
-        <f aca="false">P30+O31</f>
+        <f aca="false">O23-R31</f>
         <v>0</v>
       </c>
       <c r="T31" s="24" t="n">
-        <f aca="false">O23-P31</f>
-        <v>56</v>
+        <f aca="false">O23-S31</f>
+        <v>0</v>
       </c>
       <c r="U31" s="33"/>
     </row>
@@ -2246,19 +2330,27 @@
       <c r="N32" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="23"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
+      <c r="O32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="24" t="n">
+        <f aca="false">P31+O32</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="24" t="n">
+        <f aca="false">I23-P32</f>
+        <v>0</v>
+      </c>
       <c r="R32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S32" s="24" t="n">
-        <f aca="false">P31+O32</f>
+        <f aca="false">O23-R32</f>
         <v>0</v>
       </c>
       <c r="T32" s="24" t="n">
-        <f aca="false">O23-P32</f>
-        <v>56</v>
+        <f aca="false">O23-S32</f>
+        <v>0</v>
       </c>
       <c r="U32" s="33"/>
     </row>
@@ -2301,19 +2393,27 @@
       <c r="N33" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="23"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="24"/>
+      <c r="O33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="24" t="n">
+        <f aca="false">P32+O33</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="24" t="n">
+        <f aca="false">I23-P33</f>
+        <v>0</v>
+      </c>
       <c r="R33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S33" s="24" t="n">
-        <f aca="false">P32+O33</f>
+        <f aca="false">O23-R33</f>
         <v>0</v>
       </c>
       <c r="T33" s="24" t="n">
-        <f aca="false">O23-P33</f>
-        <v>56</v>
+        <f aca="false">O23-S33</f>
+        <v>0</v>
       </c>
       <c r="U33" s="33"/>
     </row>
@@ -2356,19 +2456,27 @@
       <c r="N34" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="23"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
+      <c r="O34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="24" t="n">
+        <f aca="false">P33+O34</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="24" t="n">
+        <f aca="false">I23-P34</f>
+        <v>0</v>
+      </c>
       <c r="R34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S34" s="24" t="n">
-        <f aca="false">P33+O34</f>
+        <f aca="false">O23-R34</f>
         <v>0</v>
       </c>
       <c r="T34" s="24" t="n">
-        <f aca="false">O23-P34</f>
-        <v>56</v>
+        <f aca="false">O23-S34</f>
+        <v>0</v>
       </c>
       <c r="U34" s="33"/>
     </row>
@@ -2411,19 +2519,27 @@
       <c r="N35" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="23"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
+      <c r="O35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="24" t="n">
+        <f aca="false">P34+O35</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="24" t="n">
+        <f aca="false">I23-P35</f>
+        <v>0</v>
+      </c>
       <c r="R35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S35" s="24" t="n">
-        <f aca="false">P34+O35</f>
+        <f aca="false">O23-R35</f>
         <v>0</v>
       </c>
       <c r="T35" s="24" t="n">
-        <f aca="false">O23-P35</f>
-        <v>56</v>
+        <f aca="false">O23-S35</f>
+        <v>0</v>
       </c>
       <c r="U35" s="33"/>
     </row>
@@ -2466,19 +2582,27 @@
       <c r="N36" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="23"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
+      <c r="O36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="24" t="n">
+        <f aca="false">P35+O36</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="24" t="n">
+        <f aca="false">I23-P36</f>
+        <v>0</v>
+      </c>
       <c r="R36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S36" s="24" t="n">
-        <f aca="false">P35+O36</f>
+        <f aca="false">O23-R36</f>
         <v>0</v>
       </c>
       <c r="T36" s="24" t="n">
-        <f aca="false">O23-P36</f>
-        <v>56</v>
+        <f aca="false">O23-S36</f>
+        <v>0</v>
       </c>
       <c r="U36" s="33"/>
     </row>
@@ -2521,19 +2645,27 @@
       <c r="N37" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="23"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
+      <c r="O37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="24" t="n">
+        <f aca="false">P36+O37</f>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="24" t="n">
+        <f aca="false">I23-P37</f>
+        <v>0</v>
+      </c>
       <c r="R37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S37" s="24" t="n">
-        <f aca="false">P36+O37</f>
+        <f aca="false">O23-R37</f>
         <v>0</v>
       </c>
       <c r="T37" s="24" t="n">
-        <f aca="false">O23-P37</f>
-        <v>56</v>
+        <f aca="false">O23-S37</f>
+        <v>0</v>
       </c>
       <c r="U37" s="33"/>
     </row>
@@ -2552,25 +2684,33 @@
       <c r="L38" s="22"/>
       <c r="M38" s="22"/>
       <c r="N38" s="22"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
+      <c r="O38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="24" t="n">
+        <f aca="false">P37+O38</f>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="24" t="n">
+        <f aca="false">I23-P38</f>
+        <v>0</v>
+      </c>
       <c r="R38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="S38" s="24" t="n">
-        <f aca="false">P37+O38</f>
+        <f aca="false">O35-R38</f>
         <v>0</v>
       </c>
       <c r="T38" s="24" t="n">
-        <f aca="false">O23-P38</f>
-        <v>56</v>
+        <f aca="false">O23-S38</f>
+        <v>0</v>
       </c>
       <c r="U38" s="33"/>
     </row>
     <row r="39" customFormat="false" ht="28.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B39" s="28"/>
       <c r="C39" s="29" t="n">
@@ -2621,20 +2761,29 @@
         <f aca="false">SUM(N26:N38)</f>
         <v>0</v>
       </c>
-      <c r="O39" s="30"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
+      <c r="O39" s="30" t="n">
+        <f aca="false">SUM(O26:O38)</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="31" t="n">
+        <f aca="false">P38</f>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="31" t="n">
+        <f aca="false">Q38</f>
+        <v>0</v>
+      </c>
       <c r="R39" s="30" t="n">
         <f aca="false">SUM(O26:O38)</f>
         <v>0</v>
       </c>
       <c r="S39" s="31" t="n">
-        <f aca="false">P38</f>
+        <f aca="false">S38</f>
         <v>0</v>
       </c>
       <c r="T39" s="31" t="n">
-        <f aca="false">Q38</f>
-        <v>112</v>
+        <f aca="false">T38</f>
+        <v>0</v>
       </c>
       <c r="U39" s="34"/>
     </row>

--- a/backend/assets/report-templates/employee-leave-report-with-return-taiwan.xlsx
+++ b/backend/assets/report-templates/employee-leave-report-with-return-taiwan.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">單位：</t>
   </si>
   <si>
-    <t xml:space="preserve">補休：</t>
+    <t xml:space="preserve">特休期間：</t>
   </si>
   <si>
     <t xml:space="preserve">姓名：</t>
